--- a/04_Маршрутные_карты/Детали/МК_PSH24-036.03.xlsx
+++ b/04_Маршрутные_карты/Детали/МК_PSH24-036.03.xlsx
@@ -488,7 +488,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Стержень ⌀20, L=150</t>
+          <t>Деталь 150×20×20</t>
         </is>
       </c>
     </row>
@@ -510,7 +510,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Стержень ⌀20, L=150</t>
+          <t>Деталь 150×20×20</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
@@ -607,30 +607,30 @@
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>Распиловка прутка Ø20 в размер L=150</t>
+          <t>Заготовка по чертежу (резка/литая/сварная заготовка), комплектование</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>Ленточнопильный станок (Pilous ARG 300 / Контур-302)</t>
+          <t>Ленточнопильный станок (Pilous ARG 300 / Контур-302) / участок заготовок</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>Упоры</t>
+          <t>По технологу</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>Припуск на обработку 3 мм на сторону</t>
+          <t>Припуск на механическую обработку по технологу</t>
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.1</v>
+        <v>0.21</v>
       </c>
       <c r="H7" s="7" t="inlineStr">
         <is>
-          <t>Замер</t>
+          <t>Входной контроль</t>
         </is>
       </c>
     </row>
@@ -642,35 +642,35 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Токарная</t>
+          <t>Механическая</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Обточка по чертежу, снятие фасок</t>
+          <t>Механическая обработка по чертежу (токарно-фрезерная)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Токарно-винторезный станок 16К20 / Doosan Puma 2600</t>
+          <t>Токарно-винторезный станок 16К20 / Doosan Puma 2600 / Фрезерный обрабатывающий центр (Haas VF-2 / 6Р13)</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Цанги/патрон, резцы</t>
+          <t>Универсальная оснастка</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>Допуски по ГОСТ 25058-2016; Ra 3,2</t>
+          <t>Допуски по ГОСТ 25058-2016; Ra 6,3..12,5</t>
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.26</v>
+        <v>0.61</v>
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>Кронциркуль, микрометр</t>
+          <t>Контроль по чертежу</t>
         </is>
       </c>
     </row>
@@ -687,7 +687,7 @@
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
-          <t>Зачистка, притупление кромок</t>
+          <t>Снятие заусенцев, зачистка</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
@@ -706,7 +706,7 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
@@ -761,7 +761,7 @@
         </is>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.47</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="13">
